--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -1697,13 +1697,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1719,10 +1720,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>When it is missing</t>
+          <t>Test</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>When it fails</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
         </is>
@@ -1741,10 +1747,15 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>The value is filled</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>Exception: the record never merges and never stops the run; fix or ignore it</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>quality.gleif.level1.v1.checks[0]</t>
         </is>
@@ -1828,7 +1839,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>A copy for matching only: upper case, USPS street words, no suite, 5-digit ZIP</t>
+          <t>Keeps a copy for matching only: upper case, USPS street words, no suite, 5-digit ZIP</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1861,7 +1872,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>A copy for matching only: upper case, USPS street words, no suite, 5-digit ZIP</t>
+          <t>Keeps a copy for matching only: upper case, USPS street words, no suite, 5-digit ZIP</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2072,13 +2083,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2089,15 +2101,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Dataset</t>
+          <t>MDM field</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Rank (1 wins)</t>
+          <t>Filled by, first wins</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Winner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rules path</t>
         </is>
@@ -2111,15 +2128,371 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>gleif_entity_creation_date</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>gleif_entity_status</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>gleif_initial_registration</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>gleif_last_update</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>gleif_legal_form</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>gleif_managing_lou</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>gleif_next_renewal</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>gleif_registration_authority</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>gleif_registration_authority_entity_id</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>gleif_registration_status</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>gleif_validation_source</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>merge/kinds/company.yaml defaults.sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>sec.submissions.company.v1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
@@ -2183,7 +2556,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2201,7 +2574,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2219,7 +2592,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2237,7 +2610,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2255,7 +2628,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2273,7 +2646,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2291,7 +2664,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2309,7 +2682,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2327,7 +2700,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2345,7 +2718,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2363,7 +2736,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2381,7 +2754,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -2083,14 +2083,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="43" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2116,6 +2117,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Rules path</t>
         </is>
       </c>
@@ -2143,6 +2149,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2170,6 +2181,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2197,6 +2213,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2224,6 +2245,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2251,6 +2277,11 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2278,6 +2309,11 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2305,6 +2341,11 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2332,6 +2373,11 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2359,6 +2405,11 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2386,6 +2437,11 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2413,6 +2469,11 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2440,6 +2501,11 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2467,6 +2533,11 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>
       </c>
@@ -2493,6 +2564,11 @@
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Kind default</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>outside_approved_company_scope, unsupported_identity_kind, reported_parent_exception, quality_name_present</t>
+          <t>outside_approved_company_scope, unsupported_identity_kind, reported_parent_exception, invalid_lei, invalid_lei_checksum, quality_name_present</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>outside_approved_company_scope, unsupported_identity_kind, reported_parent_exception</t>
+          <t>outside_approved_company_scope, unsupported_identity_kind, reported_parent_exception, invalid_lei, invalid_lei_checksum</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>outside_approved_company_scope, unsupported_identity_kind, reported_parent_exception</t>
+          <t>outside_approved_company_scope, unsupported_identity_kind, reported_parent_exception, invalid_lei, invalid_lei_checksum</t>
         </is>
       </c>
     </row>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,14 +710,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1570,20 +1570,52 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Link from gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Link to gleif.level1.v1</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,14 +710,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1560,62 +1560,158 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>gleif.relationships.v1</t>
+          <t>gleif.level1.v1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+          <t>relationship SUCCESSOR_ENTITY</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>item.SuccessorLEI.$</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Link from gleif.level1.v1</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Entity.SuccessorEntity</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>One link per item (item.)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Entity.LegalEntityEvents.LegalEntityEvent</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>The first item where @event_status = COMPLETED; AffectedFields.AffectedField.$ = item.SuccessorLEI.$ (event.)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>gleif.relationships.v1</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Link from gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Link to gleif.level1.v1</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -1644,7 +1644,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>The first item where @event_status = COMPLETED; AffectedFields.AffectedField.$ = item.SuccessorLEI.$ (event.)</t>
+          <t>The first item where @event_status = COMPLETED; LegalEntityEventType.$ = MERGERS_AND_ACQUISITIONS, ABSORPTION, DEMERGER, BREAKUP, SPINOFF, ACQUISITION_BRANCH; AffectedFields.AffectedField.$ = the value at item.SuccessorLEI.$ (event.)</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,14 +710,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
     <col width="62" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1560,62 +1560,158 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>gleif.relationships.v1</t>
+          <t>gleif.level1.v1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+          <t>relationship SUCCESSOR_ENTITY</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>item.SuccessorLEI.$</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Link from gleif.level1.v1</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Entity.SuccessorEntity</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>One link per item (item.)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Entity.LegalEntityEvents.LegalEntityEvent</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>The first item where @event_status = COMPLETED; LegalEntityEventType.$ = MERGERS_AND_ACQUISITIONS, ABSORPTION, DEMERGER, BREAKUP, SPINOFF, ACQUISITION_BRANCH; AffectedFields.AffectedField.$ = the value at item.SuccessorLEI.$ (event.)</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>gleif.relationships.v1</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Link from gleif.level1.v1</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Link to gleif.level1.v1</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -1800,7 +1800,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No: lookup only</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -2216,7 +2216,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custody.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -2216,7 +2216,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>RelationshipRecord.Relationship.StartNode.NodeID.$</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>RelationshipRecord.Relationship.EndNode.NodeID.$</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1712,6 +1712,38 @@
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>RelationshipRecord.Relationship.RelationshipPeriods.RelationshipPeriod</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>The first item where PeriodType.$ = RELATIONSHIP_PERIOD (period.)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.name</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.name</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.address</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.jurisdiction</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.jurisdiction</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_legal_form</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_legal_form</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_entity_status</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_entity_status</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_registration_status</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_status</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_initial_registration</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_initial_registration</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_last_update</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_last_update</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_next_renewal</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_next_renewal</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_managing_lou</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_managing_lou</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_validation_source</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_validation_source</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_registration_authority</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_authority</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_registration_authority_entity_id</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_authority_entity_id</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.fields.gleif_entity_creation_date</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_entity_creation_date</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_postal_code</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_postal_code</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_country</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_country</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.matching.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
         </is>
       </c>
     </row>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1730,20 +1730,84 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>interval</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>invalid_relationship_interval</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Sets the record aside when the link has no start, or ends before it starts</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>invalid_relationship_status_interval</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Sets the record aside when the status is not allowed, or needs an end it lacks</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>gleif.relationships.v1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>period</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>RelationshipRecord.Relationship.RelationshipPeriods.RelationshipPeriod</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>The first item where PeriodType.$ = RELATIONSHIP_PERIOD (period.)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1317,13 +1317,13 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>headquarters_postal_code</t>
+          <t>nport_issuer</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.PostalCode.$</t>
+          <t>nport_issuer</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_postal_code</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.nport_issuer</t>
         </is>
       </c>
     </row>
@@ -1345,23 +1345,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>headquarters_country</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.Country.$</t>
+          <t>item.SuccessorLEI.$</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_country</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -1373,27 +1377,27 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>headquarters_address</t>
+          <t>relationship SUCCESSOR_ENTITY</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>street</t>
+          <t>each</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.FirstAddressLine.$</t>
+          <t>Entity.SuccessorEntity</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>One link per item (item.)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -1405,409 +1409,185 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>headquarters_address</t>
+          <t>relationship SUCCESSOR_ENTITY</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>street2</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.AdditionalAddressLine (lines)</t>
+          <t>Entity.LegalEntityEvents.LegalEntityEvent</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>The first item where @event_status = COMPLETED; LegalEntityEventType.$ = MERGERS_AND_ACQUISITIONS, ABSORPTION, DEMERGER, BREAKUP, SPINOFF, ACQUISITION_BRANCH; AffectedFields.AffectedField.$ = the value at item.SuccessorLEI.$ (event.)</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>headquarters_address</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>city</t>
+          <t>from</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.City.$</t>
+          <t>RelationshipRecord.Relationship.StartNode.NodeID.$</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>Link from gleif.level1.v1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>headquarters_address</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.Region.$</t>
+          <t>RelationshipRecord.Relationship.EndNode.NodeID.$</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>headquarters_address</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>postcode</t>
+          <t>interval</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.PostalCode.$</t>
+          <t>invalid_relationship_interval</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>Sets the record aside when the link has no start, or ends before it starts</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>headquarters_address</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Entity.HeadquartersAddress.Country.$</t>
+          <t>invalid_relationship_status_interval</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>Sets the record aside when the status is not allowed, or needs an end it lacks</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.headquarters_address</t>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>relationship SUCCESSOR_ENTITY</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>item.SuccessorLEI.$</t>
+          <t>RelationshipRecord.Relationship.RelationshipPeriods.RelationshipPeriod</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Link to gleif.level1.v1</t>
+          <t>The first item where PeriodType.$ = RELATIONSHIP_PERIOD (period.)</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>relationship SUCCESSOR_ENTITY</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>each</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Entity.SuccessorEntity</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>One link per item (item.)</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>relationship SUCCESSOR_ENTITY</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>event</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Entity.LegalEntityEvents.LegalEntityEvent</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>The first item where @event_status = COMPLETED; LegalEntityEventType.$ = MERGERS_AND_ACQUISITIONS, ABSORPTION, DEMERGER, BREAKUP, SPINOFF, ACQUISITION_BRANCH; AffectedFields.AffectedField.$ = the value at item.SuccessorLEI.$ (event.)</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>from</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>RelationshipRecord.Relationship.StartNode.NodeID.$</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Link from gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>RelationshipRecord.Relationship.EndNode.NodeID.$</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Link to gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>interval</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>invalid_relationship_interval</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Sets the record aside when the link has no start, or ends before it starts</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>invalid_relationship_status_interval</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Sets the record aside when the status is not allowed, or needs an end it lacks</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>RelationshipRecord.Relationship.RelationshipPeriods.RelationshipPeriod</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>The first item where PeriodType.$ = RELATIONSHIP_PERIOD (period.)</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
@@ -1896,7 +1676,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>No: lookup only</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1121,13 +1121,13 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>gleif_last_update</t>
+          <t>gleif_managing_lou</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Registration.LastUpdateDate.$</t>
+          <t>Registration.ManagingLOU.$</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_last_update</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_managing_lou</t>
         </is>
       </c>
     </row>
@@ -1149,13 +1149,13 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>gleif_next_renewal</t>
+          <t>gleif_validation_source</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Registration.NextRenewalDate.$</t>
+          <t>Registration.ValidationSources.$</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_next_renewal</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_validation_source</t>
         </is>
       </c>
     </row>
@@ -1177,13 +1177,13 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>gleif_managing_lou</t>
+          <t>gleif_registration_authority</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Registration.ManagingLOU.$</t>
+          <t>Entity.RegistrationAuthority.RegistrationAuthorityID.$</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_managing_lou</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_authority</t>
         </is>
       </c>
     </row>
@@ -1205,13 +1205,13 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gleif_validation_source</t>
+          <t>gleif_registration_authority_entity_id</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Registration.ValidationSources.$</t>
+          <t>Entity.RegistrationAuthority.RegistrationAuthorityEntityID.$</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_validation_source</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_authority_entity_id</t>
         </is>
       </c>
     </row>
@@ -1233,13 +1233,13 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_authority</t>
+          <t>gleif_entity_creation_date</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Entity.RegistrationAuthority.RegistrationAuthorityID.$</t>
+          <t>Entity.EntityCreationDate.$</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_authority</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_entity_creation_date</t>
         </is>
       </c>
     </row>
@@ -1261,23 +1261,23 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_authority_entity_id</t>
+          <t>nport_issuer</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Entity.RegistrationAuthority.RegistrationAuthorityEntityID.$</t>
+          <t>nport_issuer</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>Matching only</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_registration_authority_entity_id</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.nport_issuer</t>
         </is>
       </c>
     </row>
@@ -1289,23 +1289,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>gleif_entity_creation_date</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>to</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Entity.EntityCreationDate.$</t>
+          <t>item.SuccessorLEI.$</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MDM field</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.fields.object.fields.gleif_entity_creation_date</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -1317,23 +1321,27 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>nport_issuer</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr"/>
+          <t>relationship SUCCESSOR_ENTITY</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>nport_issuer</t>
+          <t>Entity.SuccessorEntity</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Matching only</t>
+          <t>One link per item (item.)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.reading.read.tables.mapped.columns.matching.object.fields.nport_issuer</t>
+          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -1350,17 +1358,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>event</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>item.SuccessorLEI.$</t>
+          <t>Entity.LegalEntityEvents.LegalEntityEvent</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Link to gleif.level1.v1</t>
+          <t>The first item where @event_status = COMPLETED; LegalEntityEventType.$ = MERGERS_AND_ACQUISITIONS, ABSORPTION, DEMERGER, BREAKUP, SPINOFF, ACQUISITION_BRANCH; AffectedFields.AffectedField.$ = the value at item.SuccessorLEI.$ (event.)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1372,64 +1380,64 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>relationship SUCCESSOR_ENTITY</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>each</t>
+          <t>from</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Entity.SuccessorEntity</t>
+          <t>RelationshipRecord.Relationship.StartNode.NodeID.$</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>One link per item (item.)</t>
+          <t>Link from gleif.level1.v1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>gleif.relationships.v1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>relationship SUCCESSOR_ENTITY</t>
+          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>to</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Entity.LegalEntityEvents.LegalEntityEvent</t>
+          <t>RelationshipRecord.Relationship.EndNode.NodeID.$</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>The first item where @event_status = COMPLETED; LegalEntityEventType.$ = MERGERS_AND_ACQUISITIONS, ABSORPTION, DEMERGER, BREAKUP, SPINOFF, ACQUISITION_BRANCH; AffectedFields.AffectedField.$ = the value at item.SuccessorLEI.$ (event.)</t>
+          <t>Link to gleif.level1.v1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>mdm.gleif.level1.v1.contract.adapter.relationships</t>
+          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1454,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>from</t>
+          <t>interval</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>RelationshipRecord.Relationship.StartNode.NodeID.$</t>
+          <t>invalid_relationship_interval</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Link from gleif.level1.v1</t>
+          <t>Sets the record aside when the link has no start, or ends before it starts</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1478,17 +1486,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>to</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RelationshipRecord.Relationship.EndNode.NodeID.$</t>
+          <t>invalid_relationship_status_interval</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Link to gleif.level1.v1</t>
+          <t>Sets the record aside when the status is not allowed, or needs an end it lacks</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1510,84 +1518,20 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>interval</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>invalid_relationship_interval</t>
+          <t>RelationshipRecord.Relationship.RelationshipPeriods.RelationshipPeriod</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Sets the record aside when the link has no start, or ends before it starts</t>
+          <t>The first item where PeriodType.$ = RELATIONSHIP_PERIOD (period.)</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>invalid_relationship_status_interval</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Sets the record aside when the status is not allowed, or needs an end it lacks</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>gleif.relationships.v1</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>relationship IS_DIRECTLY_CONSOLIDATED_BY, IS_ULTIMATELY_CONSOLIDATED_BY</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>RelationshipRecord.Relationship.RelationshipPeriods.RelationshipPeriod</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>The first item where PeriodType.$ = RELATIONSHIP_PERIOD (period.)</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>mdm.gleif.relationships.v1.contract.adapter.relationships</t>
         </is>
@@ -2087,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2266,7 +2210,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>gleif_last_update</t>
+          <t>gleif_legal_form</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2298,7 +2242,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>gleif_legal_form</t>
+          <t>gleif_managing_lou</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2330,7 +2274,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>gleif_managing_lou</t>
+          <t>gleif_registration_authority</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2362,7 +2306,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>gleif_next_renewal</t>
+          <t>gleif_registration_authority_entity_id</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2394,7 +2338,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_authority</t>
+          <t>gleif_registration_status</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2426,7 +2370,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_authority_entity_id</t>
+          <t>gleif_validation_source</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2458,7 +2402,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>gleif_registration_status</t>
+          <t>jurisdiction</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2490,17 +2434,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>gleif_validation_source</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>gleif.level1.v1</t>
+          <t>sec.submissions.company.v1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2509,70 +2453,6 @@
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>jurisdiction</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>gleif.level1.v1</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>merge/kinds/company.yaml defaults.sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1, gleif.level1.v1, iapd.adv.filings.v1, iapd.adv.custodians.v1, sec.nport.registrant.v1</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>sec.submissions.company.v1</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Kind default</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>merge/kinds/company.yaml defaults.sources</t>
         </is>

--- a/rules/sources/gleif/MAPPING.xlsx
+++ b/rules/sources/gleif/MAPPING.xlsx
@@ -13,7 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critical data elements" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data quality" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Who wins" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline targets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline steps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2469,6 +2471,402 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Run checks</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lease seconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Heartbeat seconds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>umbrellas</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>manifest.hash, work.accounting, journal.delivered</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.umbrellas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Checks</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rules path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>mdm.prepare</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.prepared</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>mdm.merge</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>prepare</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{batch_id}</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>mdm:consumer:{consumer}</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, mdm.committed</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mastering</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>journal.record</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>merge</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, journal.recorded</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.mastering.steps[3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>umbrellas</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>pairs</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>source.read</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, source.output</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.umbrellas.steps[0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>umbrellas</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>processed</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>journal.record</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>pairs</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>{unit}</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>artifact:{destination}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>input.hash, output.receipt, journal.recorded</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>bookkeeping.targets.umbrellas.steps[1]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
